--- a/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,65</t>
+          <t>-0,8; 4,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,35</t>
+          <t>-1,61; 5,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,26</t>
+          <t>-2,21; 1,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,01</t>
+          <t>0,12; 8,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,19; 1086,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,5</t>
+          <t>-5,55; -0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,58</t>
+          <t>-2,93; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,22</t>
+          <t>-1,55; 3,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,77</t>
+          <t>-3,94; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-94,64; 12,5</t>
+          <t>-94,75; 4,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,37; 255,95</t>
+          <t>-71,44; 250,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 574,86</t>
+          <t>-79,86; 558,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 158,5</t>
+          <t>-72,73; 168,52</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -0,93</t>
+          <t>-8,86; -0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,37</t>
+          <t>-5,43; 1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,89</t>
+          <t>-1,1; 4,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 2,28</t>
+          <t>-6,23; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 863,92</t>
+          <t>-67,43; 794,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,02; 69,28</t>
+          <t>-69,56; 42,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,63</t>
+          <t>-3,06; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 1,17</t>
+          <t>-7,64; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,61</t>
+          <t>-5,35; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 2,89</t>
+          <t>-7,01; 2,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 276,52</t>
+          <t>-72,88; 230,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 43,62</t>
+          <t>-83,4; 55,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 166,5</t>
+          <t>-73,64; 150,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 55,74</t>
+          <t>-56,95; 49,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,1</t>
+          <t>-3,54; -0,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,04</t>
+          <t>-2,61; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,18</t>
+          <t>-1,2; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,41</t>
+          <t>-3,54; 1,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -0,71</t>
+          <t>-74,73; -7,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 38,77</t>
+          <t>-57,32; 43,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 138,67</t>
+          <t>-44,88; 137,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 28,75</t>
+          <t>-45,97; 26,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,53</t>
+          <t>-1,52; 4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,5</t>
+          <t>-1,66; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,27</t>
+          <t>-2,25; 1,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,48</t>
+          <t>0,65; 7,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 1086,04</t>
+          <t>-79,0; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,6</t>
+          <t>-6,19; -0,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,64</t>
+          <t>-2,78; 3,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,09</t>
+          <t>-1,7; 2,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,86</t>
+          <t>-4,03; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-94,75; 4,99</t>
+          <t>-100,0; -7,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,44; 250,46</t>
+          <t>-69,52; 259,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,86; 558,98</t>
+          <t>-84,64; 632,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 168,52</t>
+          <t>-70,96; 159,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -0,85</t>
+          <t>-9,08; -1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,38</t>
+          <t>-5,33; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,59</t>
+          <t>-1,2; 5,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,63</t>
+          <t>-6,05; 1,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 63,54</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,43; 794,95</t>
+          <t>-63,58; 914,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 42,7</t>
+          <t>-68,72; 44,66</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,47</t>
+          <t>-2,67; 3,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 1,49</t>
+          <t>-7,93; 0,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,17</t>
+          <t>-6,11; 3,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 2,83</t>
+          <t>-6,39; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,88; 230,8</t>
+          <t>-66,13; 304,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,4; 55,03</t>
+          <t>-84,44; 41,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,64; 150,53</t>
+          <t>-77,76; 142,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 49,16</t>
+          <t>-56,33; 54,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,31</t>
+          <t>-3,44; -0,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,08</t>
+          <t>-2,45; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,97</t>
+          <t>-1,13; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,22</t>
+          <t>-3,53; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -7,79</t>
+          <t>-74,46; -2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 43,35</t>
+          <t>-55,34; 42,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 137,13</t>
+          <t>-38,88; 127,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 26,83</t>
+          <t>-46,3; 25,01</t>
         </is>
       </c>
     </row>
